--- a/Cleaned Data/Cleaned_Districts.xlsx
+++ b/Cleaned Data/Cleaned_Districts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\End-user\Documents\Web_Lab2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\End-user\Documents\Web_Lab2\stc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C275F0F0-8A01-43AD-8C26-2BC99F82302A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{88D8BC6E-6A44-4A12-AE94-EB7E43BA3638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="276">
   <si>
     <t>District_ar</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Longitude</t>
   </si>
   <si>
-    <t>Average Price</t>
-  </si>
-  <si>
     <t>حي الخالدية الشمالية</t>
   </si>
   <si>
@@ -317,12 +314,6 @@
     <t>2nd Industrial City</t>
   </si>
   <si>
-    <t>مطار الملك فهد الدولي</t>
-  </si>
-  <si>
-    <t>King Fahd International Airport</t>
-  </si>
-  <si>
     <t>حي الخضرية</t>
   </si>
   <si>
@@ -473,12 +464,6 @@
     <t>Al Iskan Dist.</t>
   </si>
   <si>
-    <t>مدينة الملك فيصل الجامعية</t>
-  </si>
-  <si>
-    <t>King Faisal University</t>
-  </si>
-  <si>
     <t>حي الخالدية الجنوبية</t>
   </si>
   <si>
@@ -875,23 +860,17 @@
     <t>Gharb Adh Dhahran Dist.</t>
   </si>
   <si>
-    <t>جامعة الملك فهد للبترول والمعادن</t>
-  </si>
-  <si>
-    <t>King Fahd University Of Petroleum And Minerals</t>
-  </si>
-  <si>
-    <t>أجيال</t>
-  </si>
-  <si>
-    <t>Ajyal</t>
+    <t>Residential Average Price</t>
+  </si>
+  <si>
+    <t>Commercial Average Price</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -922,6 +901,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -937,7 +928,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1001,25 +992,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1032,9 +1010,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1340,7 +1322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J145"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.88671875" bestFit="1" customWidth="1"/>
@@ -1370,23 +1352,26 @@
         <v>5</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>6</v>
+        <v>275</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>274</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="4"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2">
         <v>26.410412699999998</v>
@@ -1397,19 +1382,22 @@
       <c r="G2" s="9">
         <v>667</v>
       </c>
+      <c r="H2">
+        <v>22464</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2">
         <v>26.397975200000001</v>
@@ -1420,19 +1408,22 @@
       <c r="G3" s="2">
         <v>620</v>
       </c>
+      <c r="H3">
+        <v>15391</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2">
         <v>26.404985100000001</v>
@@ -1443,19 +1434,22 @@
       <c r="G4" s="2">
         <v>1013</v>
       </c>
+      <c r="H4" s="12">
+        <v>12000</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2">
         <v>26.436741600000001</v>
@@ -1466,19 +1460,22 @@
       <c r="G5" s="2">
         <v>661</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H5" s="11">
+        <v>10856</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2">
         <v>26.436117200000002</v>
@@ -1489,19 +1486,22 @@
       <c r="G6" s="2">
         <v>631</v>
       </c>
+      <c r="H6" s="16">
+        <v>14747</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2">
         <v>26.434518799999999</v>
@@ -1512,19 +1512,22 @@
       <c r="G7" s="2">
         <v>497</v>
       </c>
+      <c r="H7" s="11">
+        <v>12345</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2">
         <v>26.436081300000001</v>
@@ -1535,19 +1538,22 @@
       <c r="G8" s="2">
         <v>500</v>
       </c>
+      <c r="H8" s="11">
+        <v>10940</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2">
         <v>26.4329024</v>
@@ -1558,19 +1564,22 @@
       <c r="G9" s="2">
         <v>343</v>
       </c>
+      <c r="H9" s="11">
+        <v>11495</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2">
         <v>26.445759800000001</v>
@@ -1581,19 +1590,22 @@
       <c r="G10" s="2">
         <v>906</v>
       </c>
+      <c r="H10" s="11">
+        <v>12035</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2">
         <v>26.4325765</v>
@@ -1604,19 +1616,22 @@
       <c r="G11" s="2">
         <v>614</v>
       </c>
+      <c r="H11" s="11">
+        <v>16008.65</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2">
         <v>26.4478875</v>
@@ -1627,19 +1642,22 @@
       <c r="G12" s="2">
         <v>1816</v>
       </c>
+      <c r="H12" s="11">
+        <v>16229</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2">
         <v>26.474944399999998</v>
@@ -1650,19 +1668,22 @@
       <c r="G13" s="2">
         <v>616</v>
       </c>
+      <c r="H13" s="11">
+        <v>25227</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2">
         <v>26.370633399999999</v>
@@ -1673,19 +1694,22 @@
       <c r="G14" s="2">
         <v>924</v>
       </c>
+      <c r="H14" s="11">
+        <v>19546</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2">
         <v>26.433656899999999</v>
@@ -1696,19 +1720,22 @@
       <c r="G15" s="2">
         <v>630</v>
       </c>
+      <c r="H15" s="11">
+        <v>17017</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2">
         <v>26.452282400000001</v>
@@ -1719,19 +1746,22 @@
       <c r="G16" s="2">
         <v>767</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16" s="11">
+        <v>18615</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2">
         <v>26.456129000000001</v>
@@ -1742,19 +1772,22 @@
       <c r="G17" s="2">
         <v>520</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17" s="11">
+        <v>15499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2">
         <v>26.411556999999998</v>
@@ -1765,19 +1798,22 @@
       <c r="G18" s="2">
         <v>573</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18" s="11">
+        <v>18038</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2">
         <v>26.377731900000001</v>
@@ -1788,19 +1824,22 @@
       <c r="G19" s="2">
         <v>596</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19" s="11">
+        <v>39438</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2">
         <v>26.413589300000002</v>
@@ -1811,19 +1850,22 @@
       <c r="G20" s="2">
         <v>734</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20" s="11">
+        <v>18277</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2">
         <v>26.384195099999999</v>
@@ -1834,19 +1876,22 @@
       <c r="G21" s="2">
         <v>1638</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21" s="11">
+        <v>38979</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" s="2">
         <v>26.451693800000001</v>
@@ -1857,19 +1902,22 @@
       <c r="G22" s="2">
         <v>601</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22" s="11">
+        <v>21740</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E23" s="2">
         <v>26.413333000000002</v>
@@ -1880,19 +1928,22 @@
       <c r="G23" s="2">
         <v>600</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23" s="11">
+        <v>17370</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" s="2">
         <v>26.4044007</v>
@@ -1903,19 +1954,22 @@
       <c r="G24" s="2">
         <v>673</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24" s="11">
+        <v>17343</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" s="2">
         <v>26.4452769</v>
@@ -1926,19 +1980,22 @@
       <c r="G25" s="2">
         <v>314</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25" s="11">
+        <v>10208</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2">
         <v>26.401631200000001</v>
@@ -1949,19 +2006,22 @@
       <c r="G26" s="2">
         <v>627</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26" s="11">
+        <v>17870</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E27" s="2">
         <v>26.359237700000001</v>
@@ -1972,19 +2032,22 @@
       <c r="G27" s="2">
         <v>623</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27" s="11">
+        <v>19132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E28" s="2">
         <v>26.394435000000001</v>
@@ -1995,19 +2058,22 @@
       <c r="G28" s="2">
         <v>691</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28" s="11">
+        <v>15792</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" s="2">
         <v>26.4096148</v>
@@ -2018,19 +2084,22 @@
       <c r="G29" s="2">
         <v>961</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29" s="11">
+        <v>27160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" s="2">
         <v>26.420870000000001</v>
@@ -2041,19 +2110,22 @@
       <c r="G30" s="2">
         <v>470</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30" s="11">
+        <v>12954</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" s="2">
         <v>26.433481400000002</v>
@@ -2064,19 +2136,22 @@
       <c r="G31" s="2">
         <v>439</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31" s="11">
+        <v>16804</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32" s="2">
         <v>26.424703699999998</v>
@@ -2087,19 +2162,22 @@
       <c r="G32" s="2">
         <v>491</v>
       </c>
+      <c r="H32" s="11">
+        <v>14959</v>
+      </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E33" s="2">
         <v>26.432877600000001</v>
@@ -2110,19 +2188,22 @@
       <c r="G33" s="2">
         <v>427</v>
       </c>
+      <c r="H33" s="11">
+        <v>11725</v>
+      </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E34" s="2">
         <v>26.431080099999999</v>
@@ -2133,19 +2214,22 @@
       <c r="G34" s="2">
         <v>476</v>
       </c>
+      <c r="H34" s="11">
+        <v>18516</v>
+      </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E35" s="2">
         <v>26.377633100000001</v>
@@ -2156,19 +2240,22 @@
       <c r="G35" s="2">
         <v>750</v>
       </c>
+      <c r="H35" s="11">
+        <v>24375</v>
+      </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" s="2">
         <v>26.4629072</v>
@@ -2179,19 +2266,22 @@
       <c r="G36" s="2">
         <v>422</v>
       </c>
+      <c r="H36" s="11">
+        <v>12222</v>
+      </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E37" s="2">
         <v>26.465774100000001</v>
@@ -2202,19 +2292,22 @@
       <c r="G37" s="2">
         <v>557</v>
       </c>
+      <c r="H37" s="11">
+        <v>18564</v>
+      </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E38" s="2">
         <v>26.438693300000001</v>
@@ -2225,19 +2318,22 @@
       <c r="G38" s="2">
         <v>651</v>
       </c>
+      <c r="H38" s="11">
+        <v>19638</v>
+      </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E39" s="2">
         <v>26.385856799999999</v>
@@ -2248,19 +2344,22 @@
       <c r="G39" s="2">
         <v>905</v>
       </c>
+      <c r="H39" s="11">
+        <v>24855</v>
+      </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E40" s="2">
         <v>26.384069</v>
@@ -2271,19 +2370,22 @@
       <c r="G40" s="2">
         <v>1139</v>
       </c>
+      <c r="H40" s="11">
+        <v>38179</v>
+      </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E41" s="2">
         <v>26.387218499999999</v>
@@ -2294,19 +2396,22 @@
       <c r="G41" s="2">
         <v>751</v>
       </c>
+      <c r="H41" s="11">
+        <v>22830</v>
+      </c>
     </row>
     <row r="42" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E42" s="2">
         <v>26.3644812</v>
@@ -2315,23 +2420,25 @@
         <v>50.138508299999998</v>
       </c>
       <c r="G42" s="2">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3"/>
+        <v>632</v>
+      </c>
+      <c r="H42" s="13">
+        <v>14000</v>
+      </c>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E43" s="2">
         <v>26.250202099999999</v>
@@ -2342,955 +2449,1080 @@
       <c r="G43" s="2">
         <v>1076</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H43" s="11">
+        <v>48831</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E44" s="2">
-        <v>26.476549899999998</v>
+        <v>26.447951799999998</v>
       </c>
       <c r="F44" s="2">
-        <v>49.796521900000002</v>
+        <v>50.047406899999999</v>
       </c>
       <c r="G44" s="2">
-        <v>0</v>
+        <v>711</v>
+      </c>
+      <c r="H44" s="11">
+        <v>13303</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E45" s="2">
-        <v>26.447951799999998</v>
+        <v>26.423089300000001</v>
       </c>
       <c r="F45" s="2">
-        <v>50.047406899999999</v>
+        <v>50.109830100000003</v>
       </c>
       <c r="G45" s="2">
-        <v>711</v>
+        <v>392</v>
+      </c>
+      <c r="H45" s="11">
+        <v>14506</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E46" s="2">
-        <v>26.423089300000001</v>
+        <v>26.4449583</v>
       </c>
       <c r="F46" s="2">
-        <v>50.109830100000003</v>
+        <v>50.111324099999997</v>
       </c>
       <c r="G46" s="2">
-        <v>392</v>
+        <v>508</v>
+      </c>
+      <c r="H46" s="11">
+        <v>12773</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E47" s="2">
-        <v>26.4449583</v>
+        <v>26.451419399999999</v>
       </c>
       <c r="F47" s="2">
-        <v>50.111324099999997</v>
+        <v>50.112703099999997</v>
       </c>
       <c r="G47" s="2">
-        <v>508</v>
+        <v>652</v>
+      </c>
+      <c r="H47" s="11">
+        <v>16914</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="2">
+        <v>26.478145000000001</v>
+      </c>
+      <c r="F48" s="2">
+        <v>50.132544099999997</v>
+      </c>
+      <c r="G48" s="2">
+        <v>808</v>
+      </c>
+      <c r="H48" s="11">
+        <v>23775</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" s="2">
-        <v>26.451419399999999</v>
-      </c>
-      <c r="F48" s="2">
-        <v>50.112703099999997</v>
-      </c>
-      <c r="G48" s="2">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="B49" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="2">
+        <v>26.4381138</v>
+      </c>
+      <c r="F49" s="2">
+        <v>50.038534300000002</v>
+      </c>
+      <c r="G49" s="2">
+        <v>573</v>
+      </c>
+      <c r="H49" s="11">
+        <v>17123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="2">
-        <v>26.478145000000001</v>
-      </c>
-      <c r="F49" s="2">
-        <v>50.132544099999997</v>
-      </c>
-      <c r="G49" s="2">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="2">
+        <v>26.413329099999999</v>
+      </c>
+      <c r="F50" s="2">
+        <v>50.082175800000002</v>
+      </c>
+      <c r="G50" s="2">
+        <v>621</v>
+      </c>
+      <c r="H50" s="11">
+        <v>16534</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" s="2">
-        <v>26.4381138</v>
-      </c>
-      <c r="F50" s="2">
-        <v>50.038534300000002</v>
-      </c>
-      <c r="G50" s="2">
+      <c r="B51" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="2">
+        <v>26.420591699999999</v>
+      </c>
+      <c r="F51" s="2">
+        <v>50.096559200000002</v>
+      </c>
+      <c r="G51" s="2">
+        <v>453</v>
+      </c>
+      <c r="H51" s="11">
+        <v>15122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="2">
+        <v>26.439656100000001</v>
+      </c>
+      <c r="F52" s="2">
+        <v>50.1014184</v>
+      </c>
+      <c r="G52" s="2">
+        <v>1022</v>
+      </c>
+      <c r="H52" s="11">
+        <v>12106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="2">
+        <v>26.407375399999999</v>
+      </c>
+      <c r="F53" s="2">
+        <v>50.117900300000002</v>
+      </c>
+      <c r="G53" s="2">
+        <v>614</v>
+      </c>
+      <c r="H53" s="14">
+        <v>19724</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="2">
+        <v>26.441090200000001</v>
+      </c>
+      <c r="F54" s="2">
+        <v>50.110630800000003</v>
+      </c>
+      <c r="G54" s="2">
+        <v>357</v>
+      </c>
+      <c r="H54" s="11">
+        <v>15794</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="2">
+        <v>26.471399000000002</v>
+      </c>
+      <c r="F55" s="2">
+        <v>50.092352599999998</v>
+      </c>
+      <c r="G55" s="2">
+        <v>450</v>
+      </c>
+      <c r="H55" s="11">
+        <v>17581</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="2">
+        <v>26.4703883</v>
+      </c>
+      <c r="F56" s="2">
+        <v>50.062785699999999</v>
+      </c>
+      <c r="G56" s="2">
+        <v>727</v>
+      </c>
+      <c r="H56" s="11">
+        <v>20866</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="2">
+        <v>26.462585499999999</v>
+      </c>
+      <c r="F57" s="2">
+        <v>50.078924000000001</v>
+      </c>
+      <c r="G57" s="2">
+        <v>594</v>
+      </c>
+      <c r="H57" s="11">
+        <v>21184</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="2">
+        <v>26.3710813</v>
+      </c>
+      <c r="F58" s="2">
+        <v>50.176765000000003</v>
+      </c>
+      <c r="G58" s="2">
+        <v>413</v>
+      </c>
+      <c r="H58" s="11">
+        <v>54731</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="2">
+        <v>26.441698800000001</v>
+      </c>
+      <c r="F59" s="2">
+        <v>50.185698000000002</v>
+      </c>
+      <c r="G59" s="2">
+        <v>768</v>
+      </c>
+      <c r="H59" s="11">
+        <v>24723</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="2">
+        <v>26.445684199999999</v>
+      </c>
+      <c r="F60" s="2">
+        <v>50.1615179</v>
+      </c>
+      <c r="G60" s="2">
+        <v>1088</v>
+      </c>
+      <c r="H60" s="11">
+        <v>16700</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" s="2">
+        <v>26.368779799999999</v>
+      </c>
+      <c r="F61" s="2">
+        <v>50.194286900000002</v>
+      </c>
+      <c r="G61" s="2">
+        <v>861</v>
+      </c>
+      <c r="H61" s="11">
+        <v>21495</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="2">
+        <v>26.4059952</v>
+      </c>
+      <c r="F62" s="2">
+        <v>50.184818999999997</v>
+      </c>
+      <c r="G62" s="2">
+        <v>580</v>
+      </c>
+      <c r="H62" s="11">
+        <v>24936</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="2">
+        <v>26.393687</v>
+      </c>
+      <c r="F63" s="2">
+        <v>50.0714033</v>
+      </c>
+      <c r="G63" s="2">
+        <v>743</v>
+      </c>
+      <c r="H63" s="11">
+        <v>20976</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="2">
+        <v>26.459616700000002</v>
+      </c>
+      <c r="F64" s="2">
+        <v>50.055398099999998</v>
+      </c>
+      <c r="G64" s="2">
+        <v>615</v>
+      </c>
+      <c r="H64" s="11">
+        <v>15677</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="2">
+        <v>26.457426300000002</v>
+      </c>
+      <c r="F65" s="2">
+        <v>50.071764299999998</v>
+      </c>
+      <c r="G65" s="2">
+        <v>807</v>
+      </c>
+      <c r="H65" s="11">
+        <v>17242</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="2">
+        <v>26.380880000000001</v>
+      </c>
+      <c r="F66" s="2">
+        <v>50.100430299999999</v>
+      </c>
+      <c r="G66" s="2">
+        <v>457</v>
+      </c>
+      <c r="H66" s="11">
+        <v>22323</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="2">
+        <v>26.389616</v>
+      </c>
+      <c r="F67" s="2">
+        <v>50.127290100000003</v>
+      </c>
+      <c r="G67" s="2">
+        <v>445</v>
+      </c>
+      <c r="H67" s="11">
+        <v>19135</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="2">
+        <v>26.419999199999999</v>
+      </c>
+      <c r="F68" s="2">
+        <v>50.115965500000001</v>
+      </c>
+      <c r="G68" s="2">
+        <v>252</v>
+      </c>
+      <c r="H68" s="11">
+        <v>22269</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="2">
+        <v>26.4032701</v>
+      </c>
+      <c r="F69" s="2">
+        <v>50.163573100000001</v>
+      </c>
+      <c r="G69" s="2">
+        <v>708</v>
+      </c>
+      <c r="H69" s="11">
+        <v>15484</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="2">
+        <v>26.3514743</v>
+      </c>
+      <c r="F70" s="2">
+        <v>50.099575399999999</v>
+      </c>
+      <c r="G70" s="2">
+        <v>695</v>
+      </c>
+      <c r="H70" s="11">
+        <v>27340</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" s="2">
+        <v>26.4307652</v>
+      </c>
+      <c r="F71" s="2">
+        <v>50.016582999999997</v>
+      </c>
+      <c r="G71" s="2">
+        <v>886</v>
+      </c>
+      <c r="H71" s="11">
+        <v>19292</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="2">
+        <v>26.343966099999999</v>
+      </c>
+      <c r="F72" s="2">
+        <v>50.0234527</v>
+      </c>
+      <c r="G72" s="2">
+        <v>429</v>
+      </c>
+      <c r="H72" s="11">
+        <v>20962</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="2">
+        <v>26.366856599999998</v>
+      </c>
+      <c r="F73" s="2">
+        <v>49.969709199999997</v>
+      </c>
+      <c r="G73" s="2">
+        <v>625</v>
+      </c>
+      <c r="H73" s="11">
+        <v>19595</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="2">
+        <v>26.344798900000001</v>
+      </c>
+      <c r="F74" s="2">
+        <v>49.941152000000002</v>
+      </c>
+      <c r="G74" s="2">
+        <v>590</v>
+      </c>
+      <c r="H74" s="11">
+        <v>22046</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="2">
+        <v>26.380507999999999</v>
+      </c>
+      <c r="F75" s="2">
+        <v>49.9443549</v>
+      </c>
+      <c r="G75" s="2">
+        <v>708</v>
+      </c>
+      <c r="H75" s="11">
+        <v>21854</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="2">
+        <v>26.3833898</v>
+      </c>
+      <c r="F76" s="2">
+        <v>49.973746200000001</v>
+      </c>
+      <c r="G76" s="2">
+        <v>473</v>
+      </c>
+      <c r="H76" s="11">
+        <v>20791</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="2">
+        <v>26.358447200000001</v>
+      </c>
+      <c r="F77" s="2">
+        <v>49.966459700000001</v>
+      </c>
+      <c r="G77" s="2">
         <v>573</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="2">
-        <v>26.413329099999999</v>
-      </c>
-      <c r="F51" s="2">
-        <v>50.082175800000002</v>
-      </c>
-      <c r="G51" s="2">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" s="2">
-        <v>26.420591699999999</v>
-      </c>
-      <c r="F52" s="2">
-        <v>50.096559200000002</v>
-      </c>
-      <c r="G52" s="2">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="2">
-        <v>26.439656100000001</v>
-      </c>
-      <c r="F53" s="2">
-        <v>50.1014184</v>
-      </c>
-      <c r="G53" s="2">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" s="2">
-        <v>26.407375399999999</v>
-      </c>
-      <c r="F54" s="2">
-        <v>50.117900300000002</v>
-      </c>
-      <c r="G54" s="2">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" s="2">
-        <v>26.441090200000001</v>
-      </c>
-      <c r="F55" s="2">
-        <v>50.110630800000003</v>
-      </c>
-      <c r="G55" s="2">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" s="2">
-        <v>26.471399000000002</v>
-      </c>
-      <c r="F56" s="2">
-        <v>50.092352599999998</v>
-      </c>
-      <c r="G56" s="2">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" s="2">
-        <v>26.4703883</v>
-      </c>
-      <c r="F57" s="2">
-        <v>50.062785699999999</v>
-      </c>
-      <c r="G57" s="2">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" s="2">
-        <v>26.462585499999999</v>
-      </c>
-      <c r="F58" s="2">
-        <v>50.078924000000001</v>
-      </c>
-      <c r="G58" s="2">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" s="2">
-        <v>26.3710813</v>
-      </c>
-      <c r="F59" s="2">
-        <v>50.176765000000003</v>
-      </c>
-      <c r="G59" s="2">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" s="2">
-        <v>26.441698800000001</v>
-      </c>
-      <c r="F60" s="2">
-        <v>50.185698000000002</v>
-      </c>
-      <c r="G60" s="2">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" s="2">
-        <v>26.445684199999999</v>
-      </c>
-      <c r="F61" s="2">
-        <v>50.1615179</v>
-      </c>
-      <c r="G61" s="2">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" s="2">
-        <v>26.368779799999999</v>
-      </c>
-      <c r="F62" s="2">
-        <v>50.194286900000002</v>
-      </c>
-      <c r="G62" s="2">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" s="2">
-        <v>26.4059952</v>
-      </c>
-      <c r="F63" s="2">
-        <v>50.184818999999997</v>
-      </c>
-      <c r="G63" s="2">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E64" s="2">
-        <v>26.393687</v>
-      </c>
-      <c r="F64" s="2">
-        <v>50.0714033</v>
-      </c>
-      <c r="G64" s="2">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65" s="2">
-        <v>26.459616700000002</v>
-      </c>
-      <c r="F65" s="2">
-        <v>50.055398099999998</v>
-      </c>
-      <c r="G65" s="2">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" s="2">
-        <v>26.457426300000002</v>
-      </c>
-      <c r="F66" s="2">
-        <v>50.071764299999998</v>
-      </c>
-      <c r="G66" s="2">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E67" s="2">
-        <v>26.380880000000001</v>
-      </c>
-      <c r="F67" s="2">
-        <v>50.100430299999999</v>
-      </c>
-      <c r="G67" s="2">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" s="2">
-        <v>26.389616</v>
-      </c>
-      <c r="F68" s="2">
-        <v>50.127290100000003</v>
-      </c>
-      <c r="G68" s="2">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="2">
+      <c r="H77" s="11">
+        <v>19340</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="2">
+        <v>26.380109000000001</v>
+      </c>
+      <c r="F78" s="2">
+        <v>50.0809608</v>
+      </c>
+      <c r="G78" s="2">
+        <v>661</v>
+      </c>
+      <c r="H78" s="11">
+        <v>24775</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="2">
         <v>26.419999199999999</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F79" s="2">
         <v>50.115965500000001</v>
       </c>
-      <c r="G69" s="2">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" s="2">
-        <v>26.3952031</v>
-      </c>
-      <c r="F70" s="2">
-        <v>50.194305300000003</v>
-      </c>
-      <c r="G70" s="2">
-        <v>0</v>
-      </c>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" s="2">
-        <v>26.4032701</v>
-      </c>
-      <c r="F71" s="2">
-        <v>50.163573100000001</v>
-      </c>
-      <c r="G71" s="2">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" s="2">
-        <v>26.3514743</v>
-      </c>
-      <c r="F72" s="2">
-        <v>50.099575399999999</v>
-      </c>
-      <c r="G72" s="2">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" s="2">
-        <v>26.4307652</v>
-      </c>
-      <c r="F73" s="2">
-        <v>50.016582999999997</v>
-      </c>
-      <c r="G73" s="2">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E74" s="2">
-        <v>26.343966099999999</v>
-      </c>
-      <c r="F74" s="2">
-        <v>50.0234527</v>
-      </c>
-      <c r="G74" s="2">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E75" s="2">
-        <v>26.366856599999998</v>
-      </c>
-      <c r="F75" s="2">
-        <v>49.969709199999997</v>
-      </c>
-      <c r="G75" s="2">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E76" s="2">
-        <v>26.344798900000001</v>
-      </c>
-      <c r="F76" s="2">
-        <v>49.941152000000002</v>
-      </c>
-      <c r="G76" s="2">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B77" s="2" t="s">
+      <c r="G79" s="2">
+        <v>300</v>
+      </c>
+      <c r="H79" s="11">
+        <v>26954</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="2">
+        <v>26.3417013</v>
+      </c>
+      <c r="F80" s="2">
+        <v>50.001683499999999</v>
+      </c>
+      <c r="G80" s="2">
+        <v>843</v>
+      </c>
+      <c r="H80" s="11">
+        <v>23026</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="2">
+        <v>26.345718099999999</v>
+      </c>
+      <c r="F81" s="2">
+        <v>49.973104499999998</v>
+      </c>
+      <c r="G81" s="2">
+        <v>840</v>
+      </c>
+      <c r="H81" s="11">
+        <v>20850</v>
+      </c>
+      <c r="I81" s="3"/>
+    </row>
+    <row r="82" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="2">
+        <v>26.3790157</v>
+      </c>
+      <c r="F82" s="2">
+        <v>50.099532799999999</v>
+      </c>
+      <c r="G82" s="2">
+        <v>1112</v>
+      </c>
+      <c r="H82" s="11">
+        <v>21135</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="2">
+        <v>26.426676199999999</v>
+      </c>
+      <c r="F83" s="2">
+        <v>50.1199443</v>
+      </c>
+      <c r="G83" s="2">
+        <v>902</v>
+      </c>
+      <c r="H83" s="11">
+        <v>17198</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E77" s="2">
-        <v>26.380507999999999</v>
-      </c>
-      <c r="F77" s="2">
-        <v>49.9443549</v>
-      </c>
-      <c r="G77" s="2">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
+      <c r="B84" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E78" s="2">
-        <v>26.3833898</v>
-      </c>
-      <c r="F78" s="2">
-        <v>49.973746200000001</v>
-      </c>
-      <c r="G78" s="2">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E79" s="2">
-        <v>26.358447200000001</v>
-      </c>
-      <c r="F79" s="2">
-        <v>49.966459700000001</v>
-      </c>
-      <c r="G79" s="2">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E80" s="2">
-        <v>26.476676099999999</v>
-      </c>
-      <c r="F80" s="2">
-        <v>49.928865199999997</v>
-      </c>
-      <c r="G80" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" s="2">
-        <v>26.380109000000001</v>
-      </c>
-      <c r="F81" s="2">
-        <v>50.0809608</v>
-      </c>
-      <c r="G81" s="2">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E82" s="2">
-        <v>26.419999199999999</v>
-      </c>
-      <c r="F82" s="2">
-        <v>50.115965500000001</v>
-      </c>
-      <c r="G82" s="2">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E83" s="2">
-        <v>26.3417013</v>
-      </c>
-      <c r="F83" s="2">
-        <v>50.001683499999999</v>
-      </c>
-      <c r="G83" s="2">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B84" s="2" t="s">
+      <c r="C84" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="D84" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E84" s="2">
-        <v>26.345718099999999</v>
+        <v>26.1887355</v>
       </c>
       <c r="F84" s="2">
-        <v>49.973104499999998</v>
+        <v>50.130331099999999</v>
       </c>
       <c r="G84" s="2">
-        <v>0</v>
-      </c>
-      <c r="H84" s="3"/>
+        <v>840</v>
+      </c>
+      <c r="H84" s="11">
+        <v>118373</v>
+      </c>
       <c r="I84" s="3"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J84" s="3"/>
+    </row>
+    <row r="85" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>175</v>
       </c>
@@ -3298,22 +3530,25 @@
         <v>176</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>9</v>
+        <v>174</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E85" s="2">
-        <v>26.3790157</v>
+        <v>26.3741035</v>
       </c>
       <c r="F85" s="2">
-        <v>50.099532799999999</v>
+        <v>50.2172372</v>
       </c>
       <c r="G85" s="2">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+        <v>755</v>
+      </c>
+      <c r="H85" s="11">
+        <v>102346</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>177</v>
       </c>
@@ -3321,1342 +3556,1379 @@
         <v>178</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>9</v>
+        <v>174</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E86" s="2">
-        <v>26.426676199999999</v>
+        <v>26.189494400000001</v>
       </c>
       <c r="F86" s="2">
-        <v>50.1199443</v>
+        <v>50.189994599999999</v>
       </c>
       <c r="G86" s="2">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <v>793</v>
+      </c>
+      <c r="H86" s="11">
+        <v>24613</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E87" s="2">
-        <v>26.1887355</v>
+        <v>26.241668900000001</v>
       </c>
       <c r="F87" s="2">
-        <v>50.130331099999999</v>
+        <v>50.198836999999997</v>
       </c>
       <c r="G87" s="2">
-        <v>0</v>
-      </c>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
-      <c r="J87" s="3"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+        <v>368</v>
+      </c>
+      <c r="H87" s="11">
+        <v>14623</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E88" s="2">
-        <v>26.3741035</v>
+        <v>26.309455199999999</v>
       </c>
       <c r="F88" s="2">
-        <v>50.2172372</v>
+        <v>50.1972497</v>
       </c>
       <c r="G88" s="2">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1378</v>
+      </c>
+      <c r="H88" s="11">
+        <v>43898</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E89" s="2">
-        <v>26.189494400000001</v>
+        <v>26.254189799999999</v>
       </c>
       <c r="F89" s="2">
-        <v>50.189994599999999</v>
+        <v>50.198779700000003</v>
       </c>
       <c r="G89" s="2">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+        <v>520</v>
+      </c>
+      <c r="H89" s="11">
+        <v>15066</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E90" s="2">
-        <v>26.241668900000001</v>
+        <v>26.220405</v>
       </c>
       <c r="F90" s="2">
-        <v>50.198836999999997</v>
+        <v>50.1926433</v>
       </c>
       <c r="G90" s="2">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+        <v>604</v>
+      </c>
+      <c r="H90" s="11">
+        <v>20793</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E91" s="2">
-        <v>26.309455199999999</v>
+        <v>26.351040999999999</v>
       </c>
       <c r="F91" s="2">
-        <v>50.1972497</v>
+        <v>50.197647600000003</v>
       </c>
       <c r="G91" s="2">
-        <v>1378</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+        <v>843</v>
+      </c>
+      <c r="H91" s="11">
+        <v>28866</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E92" s="2">
-        <v>26.254189799999999</v>
+        <v>26.291202599999998</v>
       </c>
       <c r="F92" s="2">
-        <v>50.198779700000003</v>
+        <v>50.213649400000001</v>
       </c>
       <c r="G92" s="2">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+      <c r="H92" s="11">
+        <v>15823</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="2">
+        <v>26.2949245</v>
+      </c>
+      <c r="F93" s="2">
+        <v>50.204144900000003</v>
+      </c>
+      <c r="G93" s="2">
+        <v>494</v>
+      </c>
+      <c r="H93" s="11">
+        <v>18438</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E93" s="2">
-        <v>26.220405</v>
-      </c>
-      <c r="F93" s="2">
-        <v>50.1926433</v>
-      </c>
-      <c r="G93" s="2">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
+      <c r="B94" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="C94" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="2">
+        <v>26.303393400000001</v>
+      </c>
+      <c r="F94" s="2">
+        <v>50.185647899999999</v>
+      </c>
+      <c r="G94" s="2">
+        <v>531</v>
+      </c>
+      <c r="H94" s="11">
+        <v>19341</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" s="2">
-        <v>26.351040999999999</v>
-      </c>
-      <c r="F94" s="2">
-        <v>50.197647600000003</v>
-      </c>
-      <c r="G94" s="2">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
+      <c r="B95" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="C95" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="2">
+        <v>26.274719699999999</v>
+      </c>
+      <c r="F95" s="2">
+        <v>50.205518900000001</v>
+      </c>
+      <c r="G95" s="2">
+        <v>469</v>
+      </c>
+      <c r="H95" s="11">
+        <v>15227</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E95" s="2">
-        <v>26.291202599999998</v>
-      </c>
-      <c r="F95" s="2">
-        <v>50.213649400000001</v>
-      </c>
-      <c r="G95" s="2">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="B96" s="2" t="s">
-        <v>98</v>
+        <v>196</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E96" s="2">
-        <v>26.2949245</v>
+        <v>26.331623100000002</v>
       </c>
       <c r="F96" s="2">
-        <v>50.204144900000003</v>
+        <v>50.209889799999999</v>
       </c>
       <c r="G96" s="2">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+        <v>626</v>
+      </c>
+      <c r="H96" s="11">
+        <v>68145</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E97" s="2">
-        <v>26.303393400000001</v>
+        <v>26.317824399999999</v>
       </c>
       <c r="F97" s="2">
-        <v>50.185647899999999</v>
+        <v>50.2198517</v>
       </c>
       <c r="G97" s="2">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+        <v>939</v>
+      </c>
+      <c r="H97" s="11">
+        <v>37028</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E98" s="2">
-        <v>26.274719699999999</v>
+        <v>26.229011400000001</v>
       </c>
       <c r="F98" s="2">
-        <v>50.205518900000001</v>
-      </c>
-      <c r="G98" s="2">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+        <v>50.2140336</v>
+      </c>
+      <c r="G98" s="15">
+        <v>1280</v>
+      </c>
+      <c r="H98" s="11">
+        <v>51563</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E99" s="2">
-        <v>26.331623100000002</v>
+        <v>26.3442121</v>
       </c>
       <c r="F99" s="2">
-        <v>50.209889799999999</v>
+        <v>50.186123199999997</v>
       </c>
       <c r="G99" s="2">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+        <v>871</v>
+      </c>
+      <c r="H99" s="11">
+        <v>67021</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>202</v>
+        <v>118</v>
       </c>
       <c r="B100" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" s="2">
+        <v>26.3343974</v>
+      </c>
+      <c r="F100" s="2">
+        <v>50.200128200000002</v>
+      </c>
+      <c r="G100" s="2">
+        <v>1421</v>
+      </c>
+      <c r="H100" s="11">
+        <v>78487</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E100" s="2">
-        <v>26.317824399999999</v>
-      </c>
-      <c r="F100" s="2">
-        <v>50.2198517</v>
-      </c>
-      <c r="G100" s="2">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
+      <c r="B101" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C101" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" s="2">
+        <v>26.317728500000001</v>
+      </c>
+      <c r="F101" s="2">
+        <v>50.200865999999998</v>
+      </c>
+      <c r="G101" s="2">
+        <v>957</v>
+      </c>
+      <c r="H101" s="11">
+        <v>46367</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E101" s="2">
-        <v>26.229011400000001</v>
-      </c>
-      <c r="F101" s="2">
-        <v>50.2140336</v>
-      </c>
-      <c r="G101" s="2">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
+      <c r="B102" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="C102" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="2">
+        <v>26.3210202</v>
+      </c>
+      <c r="F102" s="2">
+        <v>50.185889899999999</v>
+      </c>
+      <c r="G102" s="2">
+        <v>975</v>
+      </c>
+      <c r="H102" s="11">
+        <v>50926</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E102" s="2">
-        <v>26.3442121</v>
-      </c>
-      <c r="F102" s="2">
-        <v>50.186123199999997</v>
-      </c>
-      <c r="G102" s="2">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="B103" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E103" s="2">
-        <v>26.3343974</v>
+        <v>26.313092099999999</v>
       </c>
       <c r="F103" s="2">
-        <v>50.200128200000002</v>
+        <v>50.182313800000003</v>
       </c>
       <c r="G103" s="2">
-        <v>1421</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1014</v>
+      </c>
+      <c r="H103" s="11">
+        <v>31343</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E104" s="2">
-        <v>26.317728500000001</v>
+        <v>26.307382199999999</v>
       </c>
       <c r="F104" s="2">
-        <v>50.200865999999998</v>
+        <v>50.213584400000002</v>
       </c>
       <c r="G104" s="2">
+        <v>2071</v>
+      </c>
+      <c r="H104" s="11">
+        <v>35021</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" s="2">
+        <v>26.321953600000001</v>
+      </c>
+      <c r="F105" s="2">
+        <v>50.212032000000001</v>
+      </c>
+      <c r="G105" s="2">
+        <v>1902</v>
+      </c>
+      <c r="H105" s="11">
+        <v>79154</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="2">
+        <v>26.2761402</v>
+      </c>
+      <c r="F106" s="2">
+        <v>50.193713000000002</v>
+      </c>
+      <c r="G106" s="2">
+        <v>500</v>
+      </c>
+      <c r="H106" s="11">
+        <v>13642</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="2">
+        <v>26.296678400000001</v>
+      </c>
+      <c r="F107" s="2">
+        <v>50.1773004</v>
+      </c>
+      <c r="G107" s="2">
+        <v>1829</v>
+      </c>
+      <c r="H107" s="11">
+        <v>32904</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="2">
+        <v>26.256598400000001</v>
+      </c>
+      <c r="F108" s="2">
+        <v>50.207744400000003</v>
+      </c>
+      <c r="G108" s="2">
+        <v>645</v>
+      </c>
+      <c r="H108" s="11">
+        <v>24015</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" s="2">
+        <v>26.226648900000001</v>
+      </c>
+      <c r="F109" s="2">
+        <v>50.203490600000002</v>
+      </c>
+      <c r="G109" s="2">
+        <v>1969</v>
+      </c>
+      <c r="H109" s="11">
+        <v>32449</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" s="2">
+        <v>26.209509099999998</v>
+      </c>
+      <c r="F110" s="2">
+        <v>50.204353900000001</v>
+      </c>
+      <c r="G110" s="2">
+        <v>637</v>
+      </c>
+      <c r="H110" s="11">
+        <v>20088</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" s="2">
+        <v>26.208713299999999</v>
+      </c>
+      <c r="F111" s="2">
+        <v>50.188967400000003</v>
+      </c>
+      <c r="G111" s="2">
+        <v>497</v>
+      </c>
+      <c r="H111" s="11">
+        <v>39258</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="2">
+        <v>26.1447705</v>
+      </c>
+      <c r="F112" s="2">
+        <v>50.142671200000002</v>
+      </c>
+      <c r="G112" s="2">
+        <v>611</v>
+      </c>
+      <c r="H112" s="11">
+        <v>25324</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" s="2">
+        <v>26.123207300000001</v>
+      </c>
+      <c r="F113" s="2">
+        <v>50.142416099999998</v>
+      </c>
+      <c r="G113" s="2">
+        <v>484</v>
+      </c>
+      <c r="H113" s="11">
+        <v>27896</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" s="2">
+        <v>26.1195433</v>
+      </c>
+      <c r="F114" s="2">
+        <v>50.116487800000002</v>
+      </c>
+      <c r="G114" s="2">
+        <v>481</v>
+      </c>
+      <c r="H114" s="11">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" s="2">
+        <v>26.136723499999999</v>
+      </c>
+      <c r="F115" s="2">
+        <v>50.160891599999999</v>
+      </c>
+      <c r="G115" s="2">
+        <v>552</v>
+      </c>
+      <c r="H115" s="11">
+        <v>39702</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="2">
+        <v>26.3588655</v>
+      </c>
+      <c r="F116" s="2">
+        <v>50.186410100000003</v>
+      </c>
+      <c r="G116" s="2">
+        <v>720</v>
+      </c>
+      <c r="H116" s="11">
+        <v>39702</v>
+      </c>
+      <c r="I116" s="3"/>
+    </row>
+    <row r="117" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" s="2">
+        <v>26.354044500000001</v>
+      </c>
+      <c r="F117" s="2">
+        <v>50.222723799999997</v>
+      </c>
+      <c r="G117" s="2">
+        <v>1115</v>
+      </c>
+      <c r="H117" s="11">
+        <v>39702</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="2">
+        <v>26.327688299999998</v>
+      </c>
+      <c r="F118" s="2">
+        <v>50.222677699999998</v>
+      </c>
+      <c r="G118" s="2">
+        <v>1350</v>
+      </c>
+      <c r="H118" s="11">
+        <v>39702</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" s="2">
+        <v>26.245507400000001</v>
+      </c>
+      <c r="F119" s="2">
+        <v>50.214019299999997</v>
+      </c>
+      <c r="G119" s="2">
+        <v>479</v>
+      </c>
+      <c r="H119" s="11">
+        <v>39702</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="2">
+        <v>26.272320499999999</v>
+      </c>
+      <c r="F120" s="2">
+        <v>50.217933700000003</v>
+      </c>
+      <c r="G120" s="2">
+        <v>579</v>
+      </c>
+      <c r="H120" s="11">
+        <v>39702</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="2">
+        <v>26.2338311</v>
+      </c>
+      <c r="F121" s="2">
+        <v>50.216845900000003</v>
+      </c>
+      <c r="G121" s="2">
+        <v>1196</v>
+      </c>
+      <c r="H121" s="11">
+        <v>39702</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="2">
+        <v>26.189871100000001</v>
+      </c>
+      <c r="F122" s="2">
+        <v>50.178970700000001</v>
+      </c>
+      <c r="G122" s="2">
+        <v>666</v>
+      </c>
+      <c r="H122" s="11">
+        <v>39702</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="2">
+        <v>26.1546913</v>
+      </c>
+      <c r="F123" s="2">
+        <v>50.152268399999997</v>
+      </c>
+      <c r="G123" s="2">
+        <v>812</v>
+      </c>
+      <c r="H123" s="11">
+        <v>27107</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="2">
+        <v>26.151557499999999</v>
+      </c>
+      <c r="F124" s="2">
+        <v>50.121287199999998</v>
+      </c>
+      <c r="G124" s="2">
+        <v>703</v>
+      </c>
+      <c r="H124" s="11">
+        <v>23724</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" s="2">
+        <v>26.171897600000001</v>
+      </c>
+      <c r="F125" s="2">
+        <v>50.129539299999998</v>
+      </c>
+      <c r="G125" s="2">
+        <v>772</v>
+      </c>
+      <c r="H125" s="11">
+        <v>28498</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="2">
+        <v>26.196678299999999</v>
+      </c>
+      <c r="F126" s="2">
+        <v>50.145882499999999</v>
+      </c>
+      <c r="G126" s="2">
+        <v>826</v>
+      </c>
+      <c r="H126" s="11">
+        <v>29498</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="2">
+        <v>26.103638400000001</v>
+      </c>
+      <c r="F127" s="2">
+        <v>50.1458254</v>
+      </c>
+      <c r="G127" s="2">
+        <v>567</v>
+      </c>
+      <c r="H127" s="11">
+        <v>26979</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="2">
+        <v>26.317433900000001</v>
+      </c>
+      <c r="F128" s="2">
+        <v>50.163609800000003</v>
+      </c>
+      <c r="G128" s="2">
+        <v>2156</v>
+      </c>
+      <c r="H128" s="11">
+        <v>38455</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129" s="2">
+        <v>26.3373843</v>
+      </c>
+      <c r="F129" s="2">
+        <v>50.149276399999998</v>
+      </c>
+      <c r="G129" s="2">
+        <v>759</v>
+      </c>
+      <c r="H129" s="11">
+        <v>36445</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E130" s="2">
+        <v>26.344237400000001</v>
+      </c>
+      <c r="F130" s="2">
+        <v>50.1517397</v>
+      </c>
+      <c r="G130" s="2">
         <v>957</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E105" s="2">
-        <v>26.3210202</v>
-      </c>
-      <c r="F105" s="2">
-        <v>50.185889899999999</v>
-      </c>
-      <c r="G105" s="2">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E106" s="2">
-        <v>26.313092099999999</v>
-      </c>
-      <c r="F106" s="2">
-        <v>50.182313800000003</v>
-      </c>
-      <c r="G106" s="2">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E107" s="2">
-        <v>26.307382199999999</v>
-      </c>
-      <c r="F107" s="2">
-        <v>50.213584400000002</v>
-      </c>
-      <c r="G107" s="2">
-        <v>2071</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E108" s="2">
-        <v>26.321953600000001</v>
-      </c>
-      <c r="F108" s="2">
-        <v>50.212032000000001</v>
-      </c>
-      <c r="G108" s="2">
-        <v>1902</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E109" s="2">
-        <v>26.2761402</v>
-      </c>
-      <c r="F109" s="2">
-        <v>50.193713000000002</v>
-      </c>
-      <c r="G109" s="2">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E110" s="2">
-        <v>26.296678400000001</v>
-      </c>
-      <c r="F110" s="2">
-        <v>50.1773004</v>
-      </c>
-      <c r="G110" s="2">
-        <v>1829</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E111" s="2">
-        <v>26.256598400000001</v>
-      </c>
-      <c r="F111" s="2">
-        <v>50.207744400000003</v>
-      </c>
-      <c r="G111" s="2">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E112" s="2">
-        <v>26.226648900000001</v>
-      </c>
-      <c r="F112" s="2">
-        <v>50.203490600000002</v>
-      </c>
-      <c r="G112" s="2">
-        <v>1969</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E113" s="2">
-        <v>26.209509099999998</v>
-      </c>
-      <c r="F113" s="2">
-        <v>50.204353900000001</v>
-      </c>
-      <c r="G113" s="2">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E114" s="2">
-        <v>26.208713299999999</v>
-      </c>
-      <c r="F114" s="2">
-        <v>50.188967400000003</v>
-      </c>
-      <c r="G114" s="2">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E115" s="2">
-        <v>26.1447705</v>
-      </c>
-      <c r="F115" s="2">
-        <v>50.142671200000002</v>
-      </c>
-      <c r="G115" s="2">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E116" s="2">
-        <v>26.123207300000001</v>
-      </c>
-      <c r="F116" s="2">
-        <v>50.142416099999998</v>
-      </c>
-      <c r="G116" s="2">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E117" s="2">
-        <v>26.1195433</v>
-      </c>
-      <c r="F117" s="2">
-        <v>50.116487800000002</v>
-      </c>
-      <c r="G117" s="2">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E118" s="2">
-        <v>26.136723499999999</v>
-      </c>
-      <c r="F118" s="2">
-        <v>50.160891599999999</v>
-      </c>
-      <c r="G118" s="2">
-        <v>0</v>
-      </c>
-      <c r="H118" s="3"/>
-    </row>
-    <row r="119" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E119" s="2">
-        <v>26.3588655</v>
-      </c>
-      <c r="F119" s="2">
-        <v>50.186410100000003</v>
-      </c>
-      <c r="G119" s="2">
-        <v>0</v>
-      </c>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E120" s="2">
-        <v>26.354044500000001</v>
-      </c>
-      <c r="F120" s="2">
-        <v>50.222723799999997</v>
-      </c>
-      <c r="G120" s="2">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E121" s="2">
-        <v>26.327688299999998</v>
-      </c>
-      <c r="F121" s="2">
-        <v>50.222677699999998</v>
-      </c>
-      <c r="G121" s="2">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E122" s="2">
-        <v>26.245507400000001</v>
-      </c>
-      <c r="F122" s="2">
-        <v>50.214019299999997</v>
-      </c>
-      <c r="G122" s="2">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A123" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E123" s="2">
-        <v>26.272320499999999</v>
-      </c>
-      <c r="F123" s="2">
-        <v>50.217933700000003</v>
-      </c>
-      <c r="G123" s="2">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A124" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E124" s="2">
-        <v>26.2338311</v>
-      </c>
-      <c r="F124" s="2">
-        <v>50.216845900000003</v>
-      </c>
-      <c r="G124" s="2">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A125" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E125" s="2">
-        <v>26.189871100000001</v>
-      </c>
-      <c r="F125" s="2">
-        <v>50.178970700000001</v>
-      </c>
-      <c r="G125" s="2">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A126" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E126" s="2">
-        <v>26.1546913</v>
-      </c>
-      <c r="F126" s="2">
-        <v>50.152268399999997</v>
-      </c>
-      <c r="G126" s="2">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E127" s="2">
-        <v>26.151557499999999</v>
-      </c>
-      <c r="F127" s="2">
-        <v>50.121287199999998</v>
-      </c>
-      <c r="G127" s="2">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128" s="2" t="s">
+      <c r="H130" s="11">
+        <v>53339</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131" s="2">
+        <v>26.336069200000001</v>
+      </c>
+      <c r="F131" s="2">
+        <v>50.167815500000003</v>
+      </c>
+      <c r="G131" s="2">
+        <v>751</v>
+      </c>
+      <c r="H131" s="11">
+        <v>36575</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" s="2">
+        <v>26.327658799999998</v>
+      </c>
+      <c r="F132" s="2">
+        <v>50.149690900000003</v>
+      </c>
+      <c r="G132" s="2">
+        <v>652</v>
+      </c>
+      <c r="H132" s="11">
+        <v>28195</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" s="2">
+        <v>26.344217199999999</v>
+      </c>
+      <c r="F133" s="2">
+        <v>50.132736299999998</v>
+      </c>
+      <c r="G133" s="2">
+        <v>803</v>
+      </c>
+      <c r="H133" s="11">
+        <v>35682</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" s="2">
+        <v>26.3674456</v>
+      </c>
+      <c r="F134" s="2">
+        <v>50.1680639</v>
+      </c>
+      <c r="G134" s="2">
         <v>250</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E128" s="2">
-        <v>26.171897600000001</v>
-      </c>
-      <c r="F128" s="2">
-        <v>50.129539299999998</v>
-      </c>
-      <c r="G128" s="2">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B129" s="2" t="s">
+      <c r="H134" s="11">
+        <v>32770</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C135" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C129" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E129" s="2">
-        <v>26.196678299999999</v>
-      </c>
-      <c r="F129" s="2">
-        <v>50.145882499999999</v>
-      </c>
-      <c r="G129" s="2">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E130" s="2">
-        <v>26.103638400000001</v>
-      </c>
-      <c r="F130" s="2">
-        <v>50.1458254</v>
-      </c>
-      <c r="G130" s="2">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A131" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E131" s="2">
-        <v>26.317433900000001</v>
-      </c>
-      <c r="F131" s="2">
-        <v>50.163609800000003</v>
-      </c>
-      <c r="G131" s="2">
-        <v>2156</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E132" s="2">
-        <v>26.3373843</v>
-      </c>
-      <c r="F132" s="2">
-        <v>50.149276399999998</v>
-      </c>
-      <c r="G132" s="2">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A133" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E133" s="2">
-        <v>26.344237400000001</v>
-      </c>
-      <c r="F133" s="2">
-        <v>50.1517397</v>
-      </c>
-      <c r="G133" s="2">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E134" s="2">
-        <v>26.336069200000001</v>
-      </c>
-      <c r="F134" s="2">
-        <v>50.167815500000003</v>
-      </c>
-      <c r="G134" s="2">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A135" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="D135" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E135" s="2">
-        <v>26.327658799999998</v>
+        <v>26.353393400000002</v>
       </c>
       <c r="F135" s="2">
-        <v>50.149690900000003</v>
+        <v>50.130467400000001</v>
       </c>
       <c r="G135" s="2">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+        <v>398</v>
+      </c>
+      <c r="H135" s="11">
+        <v>32547</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E136" s="2">
-        <v>26.344217199999999</v>
+        <v>26.3710813</v>
       </c>
       <c r="F136" s="2">
-        <v>50.132736299999998</v>
+        <v>50.176765000000003</v>
       </c>
       <c r="G136" s="2">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+        <v>956</v>
+      </c>
+      <c r="H136" s="11">
+        <v>94449</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E137" s="2">
-        <v>26.3674456</v>
+        <v>26.372870299999999</v>
       </c>
       <c r="F137" s="2">
-        <v>50.1680639</v>
+        <v>50.104796299999997</v>
       </c>
       <c r="G137" s="2">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+        <v>634</v>
+      </c>
+      <c r="H137" s="11">
+        <v>31845</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E138" s="2">
-        <v>26.353393400000002</v>
+        <v>26.313669999999998</v>
       </c>
       <c r="F138" s="2">
-        <v>50.130467400000001</v>
+        <v>50.127029399999998</v>
       </c>
       <c r="G138" s="2">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A139" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E139" s="2">
-        <v>26.3710813</v>
-      </c>
-      <c r="F139" s="2">
-        <v>50.176765000000003</v>
-      </c>
-      <c r="G139" s="2">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A140" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E140" s="2">
-        <v>26.372870299999999</v>
-      </c>
-      <c r="F140" s="2">
-        <v>50.104796299999997</v>
-      </c>
-      <c r="G140" s="2">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A141" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E141" s="2">
-        <v>26.313669999999998</v>
-      </c>
-      <c r="F141" s="2">
-        <v>50.127029399999998</v>
-      </c>
-      <c r="G141" s="2">
         <v>439</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A142" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="B142" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="C142" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="D142" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E142" s="11">
-        <v>26.3090282</v>
-      </c>
-      <c r="F142" s="11">
-        <v>50.148699299999997</v>
-      </c>
-      <c r="G142" s="11">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="B143" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="C143" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="D143" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E143" s="12">
-        <v>26.264974800000001</v>
-      </c>
-      <c r="F143" s="12">
-        <v>50.0728188</v>
-      </c>
-      <c r="G143" s="12">
-        <v>0</v>
-      </c>
-      <c r="H143" s="10"/>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3"/>
-    <row r="145" x14ac:dyDescent="0.3"/>
+      <c r="H138" s="11">
+        <v>31625</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4671,15 +4943,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E5E8CCB3A3BFC48946126FBF49E7985" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="53c724df40420bba21f23f91232da951">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="cc771f30-18a3-4d76-953b-b5856a532230" xmlns:ns4="feedadcb-e2b1-4629-8ac0-5c501b0ae5ea" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="28fabf935d2266a833fa4e09da8b22dc" ns3:_="" ns4:_="">
     <xsd:import namespace="cc771f30-18a3-4d76-953b-b5856a532230"/>
@@ -4914,6 +5177,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73752B9C-B6C1-4437-AB00-D9CEC1523705}">
   <ds:schemaRefs>
@@ -4932,14 +5204,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACC0D173-A720-4F24-88A7-4A5F32A67DDC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04B395D8-E06E-4958-BD7D-0B7891EFC709}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4956,4 +5220,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACC0D173-A720-4F24-88A7-4A5F32A67DDC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>